--- a/outputs/UIDAI_All_Reports.xlsx
+++ b/outputs/UIDAI_All_Reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/592793ec164e2b91/Documents/UIDAI/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_C2E6684017C4643C87744C4CD53526C208277EAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5B0EDD6-DD23-4A22-B513-54FA64210146}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_C2E6684017C4643C87744C4CD53526C208277EAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF37D6B9-3CA1-4FFE-99CB-F6E527E1149C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Month_Wise_Report" sheetId="1" r:id="rId1"/>
